--- a/AdditionalData/Tables/pyramid_row_Houdin_straight_ramp_40m.xlsx
+++ b/AdditionalData/Tables/pyramid_row_Houdin_straight_ramp_40m.xlsx
@@ -46,22 +46,22 @@
     <t xml:space="preserve">distance blocks Horiz (Km)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sum force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Vert. force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Horiz. force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vert. force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horiz. force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total force blocks row (GJ)</t>
+    <t xml:space="preserve">Sum force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Vert. force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Horiz. force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vert. force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horiz. force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total force blocks row (MJ)</t>
   </si>
   <si>
     <t xml:space="preserve">% Decrement blocks</t>
@@ -637,7 +637,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3848,39 +3848,39 @@
       <c r="E59" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F59" s="0" t="n">
+      <c r="F59" s="1" t="n">
         <f aca="false">SUM(F2:F58)</f>
         <v>536361479</v>
       </c>
-      <c r="G59" s="0" t="n">
+      <c r="G59" s="1" t="n">
         <f aca="false">SUM(G2:G58)</f>
         <v>362968948</v>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="1" t="n">
         <f aca="false">SUM(H2:H58)</f>
         <v>173392563</v>
       </c>
-      <c r="I59" s="0" t="n">
+      <c r="I59" s="1" t="n">
         <f aca="false">SUM(I2:I58)</f>
         <v>262257155890</v>
       </c>
-      <c r="J59" s="0" t="n">
+      <c r="J59" s="1" t="n">
         <f aca="false">SUM(J2:J58)</f>
         <v>151896397370</v>
       </c>
-      <c r="K59" s="0" t="n">
+      <c r="K59" s="1" t="n">
         <f aca="false">SUM(K2:K58)</f>
         <v>110629087290</v>
       </c>
-      <c r="L59" s="0" t="n">
+      <c r="L59" s="1" t="n">
         <f aca="false">SUM(L2:L58)</f>
         <v>6200337790</v>
       </c>
-      <c r="M59" s="0" t="n">
+      <c r="M59" s="1" t="n">
         <f aca="false">SUM(M2:M58)</f>
         <v>2692446490</v>
       </c>
-      <c r="N59" s="0" t="n">
+      <c r="N59" s="1" t="n">
         <f aca="false">SUM(N2:N58)</f>
         <v>8892755850</v>
       </c>
